--- a/data/trans_dic/P1806_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,47</t>
+          <t>1,62; 4,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,62</t>
+          <t>5,73; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,32</t>
+          <t>4,34; 6,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,62</t>
+          <t>1,17; 2,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,73</t>
+          <t>2,66; 4,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,39</t>
+          <t>2,19; 3,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,25</t>
+          <t>2,18; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,58</t>
+          <t>5,2; 8,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,23</t>
+          <t>4,15; 6,21</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,89</t>
+          <t>1,73; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,62</t>
+          <t>4,03; 5,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,15</t>
+          <t>3,14; 4,12</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8467; 23036</t>
+          <t>8347; 23546</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43566; 65080</t>
+          <t>43292; 63607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55597; 80204</t>
+          <t>55084; 79488</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27619; 59916</t>
+          <t>26763; 59730</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61003; 105865</t>
+          <t>59479; 102533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99251; 153324</t>
+          <t>99087; 150067</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14071; 33967</t>
+          <t>14095; 32951</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34608; 56676</t>
+          <t>34331; 56919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52342; 81404</t>
+          <t>54255; 81187</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57877; 99634</t>
+          <t>59732; 101063</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147456; 205176</t>
+          <t>147119; 206093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220316; 295110</t>
+          <t>223394; 293016</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1806_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,57</t>
+          <t>1,61; 4,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,43</t>
+          <t>5,72; 8,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,26</t>
+          <t>4,22; 6,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,61</t>
+          <t>1,41; 2,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,58</t>
+          <t>3,38; 4,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,31</t>
+          <t>2,56; 3,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,1</t>
+          <t>2,15; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,62</t>
+          <t>5,1; 8,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,21</t>
+          <t>3,86; 6,01</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,93</t>
+          <t>1,85; 2,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,64</t>
+          <t>4,64; 5,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,12</t>
+          <t>3,42; 4,2</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66764</t>
+          <t>71122</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8347; 23546</t>
+          <t>9326; 24005</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43292; 63607</t>
+          <t>46950; 68835</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55084; 79488</t>
+          <t>59055; 84916</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43167</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81982</t>
+          <t>88551</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125149</t>
+          <t>132849</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26763; 59730</t>
+          <t>31544; 61333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59479; 102533</t>
+          <t>73392; 106961</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99087; 150067</t>
+          <t>112541; 156085</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65899</t>
+          <t>70772</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14095; 32951</t>
+          <t>15282; 36674</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34331; 56919</t>
+          <t>37498; 60224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54255; 81187</t>
+          <t>55830; 86873</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79007</t>
+          <t>81274</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>178806</t>
+          <t>193469</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>257813</t>
+          <t>274743</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59732; 101063</t>
+          <t>65227; 101243</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147119; 206093</t>
+          <t>172896; 217853</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223394; 293016</t>
+          <t>247848; 304607</t>
         </is>
       </c>
     </row>
